--- a/sources/table_normalization/xlsx/employment-table18.xlsx
+++ b/sources/table_normalization/xlsx/employment-table18.xlsx
@@ -229,7 +229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -238,7 +238,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -594,27 +595,27 @@
       <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="6" t="s">
+      <c r="D5" s="6"/>
+      <c r="E5" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="6" t="s">
+      <c r="F5" s="6"/>
+      <c r="G5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="6" t="s">
+      <c r="H5" s="6"/>
+      <c r="I5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5" t="s">
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="M5" s="5"/>
+      <c r="M5" s="6"/>
     </row>
     <row r="6" spans="1:13" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
